--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE96"/>
+  <dimension ref="A1:AE97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11697,6 +11697,123 @@
       <c r="AE96" t="inlineStr">
         <is>
           <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>18</v>
+      </c>
+      <c r="D97" t="n">
+        <v>17</v>
+      </c>
+      <c r="E97" t="n">
+        <v>20</v>
+      </c>
+      <c r="F97" t="n">
+        <v>22</v>
+      </c>
+      <c r="G97" t="n">
+        <v>25</v>
+      </c>
+      <c r="H97" t="n">
+        <v>25</v>
+      </c>
+      <c r="I97" t="n">
+        <v>22</v>
+      </c>
+      <c r="J97" t="n">
+        <v>22</v>
+      </c>
+      <c r="K97" t="n">
+        <v>18</v>
+      </c>
+      <c r="L97" t="n">
+        <v>12</v>
+      </c>
+      <c r="M97" t="n">
+        <v>13</v>
+      </c>
+      <c r="N97" t="n">
+        <v>12</v>
+      </c>
+      <c r="O97" t="n">
+        <v>10</v>
+      </c>
+      <c r="P97" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>14</v>
+      </c>
+      <c r="R97" t="n">
+        <v>16</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="n">
+        <v>14</v>
+      </c>
+      <c r="U97" t="n">
+        <v>12</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Пасмурно,  дождь, гроза</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
         </is>
       </c>
     </row>

--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE97"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11814,6 +11814,942 @@
       <c r="AE97" t="inlineStr">
         <is>
           <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>21</v>
+      </c>
+      <c r="D98" t="n">
+        <v>19</v>
+      </c>
+      <c r="E98" t="n">
+        <v>21</v>
+      </c>
+      <c r="F98" t="n">
+        <v>24</v>
+      </c>
+      <c r="G98" t="n">
+        <v>21</v>
+      </c>
+      <c r="H98" t="n">
+        <v>16</v>
+      </c>
+      <c r="I98" t="n">
+        <v>15</v>
+      </c>
+      <c r="J98" t="n">
+        <v>13</v>
+      </c>
+      <c r="K98" t="n">
+        <v>13</v>
+      </c>
+      <c r="L98" t="n">
+        <v>11</v>
+      </c>
+      <c r="M98" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" t="n">
+        <v>12</v>
+      </c>
+      <c r="O98" t="n">
+        <v>13</v>
+      </c>
+      <c r="P98" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>14</v>
+      </c>
+      <c r="R98" t="n">
+        <v>11</v>
+      </c>
+      <c r="S98" t="n">
+        <v>8</v>
+      </c>
+      <c r="T98" t="n">
+        <v>10</v>
+      </c>
+      <c r="U98" t="n">
+        <v>8</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Малооблачно,  дождь, гроза</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Пасмурно,  дождь</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>19</v>
+      </c>
+      <c r="C99" t="n">
+        <v>20</v>
+      </c>
+      <c r="D99" t="n">
+        <v>22</v>
+      </c>
+      <c r="E99" t="n">
+        <v>24</v>
+      </c>
+      <c r="F99" t="n">
+        <v>20</v>
+      </c>
+      <c r="G99" t="n">
+        <v>16</v>
+      </c>
+      <c r="H99" t="n">
+        <v>16</v>
+      </c>
+      <c r="I99" t="n">
+        <v>16</v>
+      </c>
+      <c r="J99" t="n">
+        <v>21</v>
+      </c>
+      <c r="K99" t="n">
+        <v>20</v>
+      </c>
+      <c r="L99" t="n">
+        <v>9</v>
+      </c>
+      <c r="M99" t="n">
+        <v>11</v>
+      </c>
+      <c r="N99" t="n">
+        <v>10</v>
+      </c>
+      <c r="O99" t="n">
+        <v>12</v>
+      </c>
+      <c r="P99" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>11</v>
+      </c>
+      <c r="R99" t="n">
+        <v>8</v>
+      </c>
+      <c r="S99" t="n">
+        <v>9</v>
+      </c>
+      <c r="T99" t="n">
+        <v>14</v>
+      </c>
+      <c r="U99" t="n">
+        <v>13</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Малооблачно,  дождь</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>20</v>
+      </c>
+      <c r="C100" t="n">
+        <v>22</v>
+      </c>
+      <c r="D100" t="n">
+        <v>24</v>
+      </c>
+      <c r="E100" t="n">
+        <v>20</v>
+      </c>
+      <c r="F100" t="n">
+        <v>17</v>
+      </c>
+      <c r="G100" t="n">
+        <v>17</v>
+      </c>
+      <c r="H100" t="n">
+        <v>18</v>
+      </c>
+      <c r="I100" t="n">
+        <v>20</v>
+      </c>
+      <c r="J100" t="n">
+        <v>21</v>
+      </c>
+      <c r="K100" t="n">
+        <v>22</v>
+      </c>
+      <c r="L100" t="n">
+        <v>12</v>
+      </c>
+      <c r="M100" t="n">
+        <v>11</v>
+      </c>
+      <c r="N100" t="n">
+        <v>13</v>
+      </c>
+      <c r="O100" t="n">
+        <v>13</v>
+      </c>
+      <c r="P100" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>9</v>
+      </c>
+      <c r="R100" t="n">
+        <v>8</v>
+      </c>
+      <c r="S100" t="n">
+        <v>11</v>
+      </c>
+      <c r="T100" t="n">
+        <v>14</v>
+      </c>
+      <c r="U100" t="n">
+        <v>14</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>Малооблачно,  дождь</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>22</v>
+      </c>
+      <c r="C101" t="n">
+        <v>25</v>
+      </c>
+      <c r="D101" t="n">
+        <v>19</v>
+      </c>
+      <c r="E101" t="n">
+        <v>17</v>
+      </c>
+      <c r="F101" t="n">
+        <v>15</v>
+      </c>
+      <c r="G101" t="n">
+        <v>17</v>
+      </c>
+      <c r="H101" t="n">
+        <v>20</v>
+      </c>
+      <c r="I101" t="n">
+        <v>19</v>
+      </c>
+      <c r="J101" t="n">
+        <v>20</v>
+      </c>
+      <c r="K101" t="n">
+        <v>21</v>
+      </c>
+      <c r="L101" t="n">
+        <v>11</v>
+      </c>
+      <c r="M101" t="n">
+        <v>13</v>
+      </c>
+      <c r="N101" t="n">
+        <v>13</v>
+      </c>
+      <c r="O101" t="n">
+        <v>11</v>
+      </c>
+      <c r="P101" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>6</v>
+      </c>
+      <c r="R101" t="n">
+        <v>9</v>
+      </c>
+      <c r="S101" t="n">
+        <v>11</v>
+      </c>
+      <c r="T101" t="n">
+        <v>10</v>
+      </c>
+      <c r="U101" t="n">
+        <v>11</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>25</v>
+      </c>
+      <c r="C102" t="n">
+        <v>19</v>
+      </c>
+      <c r="D102" t="n">
+        <v>16</v>
+      </c>
+      <c r="E102" t="n">
+        <v>15</v>
+      </c>
+      <c r="F102" t="n">
+        <v>18</v>
+      </c>
+      <c r="G102" t="n">
+        <v>20</v>
+      </c>
+      <c r="H102" t="n">
+        <v>17</v>
+      </c>
+      <c r="I102" t="n">
+        <v>18</v>
+      </c>
+      <c r="J102" t="n">
+        <v>23</v>
+      </c>
+      <c r="K102" t="n">
+        <v>21</v>
+      </c>
+      <c r="L102" t="n">
+        <v>15</v>
+      </c>
+      <c r="M102" t="n">
+        <v>13</v>
+      </c>
+      <c r="N102" t="n">
+        <v>11</v>
+      </c>
+      <c r="O102" t="n">
+        <v>8</v>
+      </c>
+      <c r="P102" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>11</v>
+      </c>
+      <c r="R102" t="n">
+        <v>11</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="n">
+        <v>12</v>
+      </c>
+      <c r="U102" t="n">
+        <v>13</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Skaidrs</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Mākoņains, neliels  lietus</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Mazmākoņains, neliels  lietus</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>Mazmākoņains, neliels lietus</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>Skaidrs</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Mazmākoņains, neliels lietus</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Mākoņains, neliels  lietus</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Mākoņains, neliels  lietus</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>Mazmākoņains, neliels  lietus</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>Mazmākoņains, neliels  lietus</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>19</v>
+      </c>
+      <c r="C103" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" t="n">
+        <v>14</v>
+      </c>
+      <c r="E103" t="n">
+        <v>17</v>
+      </c>
+      <c r="F103" t="n">
+        <v>21</v>
+      </c>
+      <c r="G103" t="n">
+        <v>16</v>
+      </c>
+      <c r="H103" t="n">
+        <v>13</v>
+      </c>
+      <c r="I103" t="n">
+        <v>12</v>
+      </c>
+      <c r="J103" t="n">
+        <v>15</v>
+      </c>
+      <c r="K103" t="n">
+        <v>15</v>
+      </c>
+      <c r="L103" t="n">
+        <v>13</v>
+      </c>
+      <c r="M103" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" t="n">
+        <v>6</v>
+      </c>
+      <c r="P103" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>11</v>
+      </c>
+      <c r="R103" t="n">
+        <v>9</v>
+      </c>
+      <c r="S103" t="n">
+        <v>8</v>
+      </c>
+      <c r="T103" t="n">
+        <v>7</v>
+      </c>
+      <c r="U103" t="n">
+        <v>11</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Облачно,  дождь</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>Пасмурно,  дождь</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>15</v>
+      </c>
+      <c r="D104" t="n">
+        <v>18</v>
+      </c>
+      <c r="E104" t="n">
+        <v>22</v>
+      </c>
+      <c r="F104" t="n">
+        <v>17</v>
+      </c>
+      <c r="G104" t="n">
+        <v>17</v>
+      </c>
+      <c r="H104" t="n">
+        <v>17</v>
+      </c>
+      <c r="I104" t="n">
+        <v>17</v>
+      </c>
+      <c r="J104" t="n">
+        <v>21</v>
+      </c>
+      <c r="K104" t="n">
+        <v>22</v>
+      </c>
+      <c r="L104" t="n">
+        <v>11</v>
+      </c>
+      <c r="M104" t="n">
+        <v>9</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4</v>
+      </c>
+      <c r="O104" t="n">
+        <v>8</v>
+      </c>
+      <c r="P104" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>10</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7</v>
+      </c>
+      <c r="S104" t="n">
+        <v>9</v>
+      </c>
+      <c r="T104" t="n">
+        <v>10</v>
+      </c>
+      <c r="U104" t="n">
+        <v>13</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>15</v>
+      </c>
+      <c r="C105" t="n">
+        <v>17</v>
+      </c>
+      <c r="D105" t="n">
+        <v>21</v>
+      </c>
+      <c r="E105" t="n">
+        <v>16</v>
+      </c>
+      <c r="F105" t="n">
+        <v>13</v>
+      </c>
+      <c r="G105" t="n">
+        <v>14</v>
+      </c>
+      <c r="H105" t="n">
+        <v>14</v>
+      </c>
+      <c r="I105" t="n">
+        <v>18</v>
+      </c>
+      <c r="J105" t="n">
+        <v>19</v>
+      </c>
+      <c r="K105" t="n">
+        <v>19</v>
+      </c>
+      <c r="L105" t="n">
+        <v>8</v>
+      </c>
+      <c r="M105" t="n">
+        <v>6</v>
+      </c>
+      <c r="N105" t="n">
+        <v>9</v>
+      </c>
+      <c r="O105" t="n">
+        <v>10</v>
+      </c>
+      <c r="P105" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>6</v>
+      </c>
+      <c r="R105" t="n">
+        <v>8</v>
+      </c>
+      <c r="S105" t="n">
+        <v>8</v>
+      </c>
+      <c r="T105" t="n">
+        <v>9</v>
+      </c>
+      <c r="U105" t="n">
+        <v>10</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Малооблачно,  дождь</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
         </is>
       </c>
     </row>

--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE105"/>
+  <dimension ref="A1:AE107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11820,68 +11820,68 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C98" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E98" t="n">
         <v>21</v>
       </c>
       <c r="F98" t="n">
+        <v>22</v>
+      </c>
+      <c r="G98" t="n">
         <v>24</v>
       </c>
-      <c r="G98" t="n">
-        <v>21</v>
-      </c>
       <c r="H98" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K98" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L98" t="n">
+        <v>13</v>
+      </c>
+      <c r="M98" t="n">
         <v>11</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>10</v>
       </c>
-      <c r="N98" t="n">
-        <v>12</v>
-      </c>
       <c r="O98" t="n">
         <v>13</v>
       </c>
       <c r="P98" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q98" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R98" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T98" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U98" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -11890,14 +11890,14 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Малооблачно,  дождь, гроза</t>
-        </is>
-      </c>
       <c r="Y98" t="inlineStr">
         <is>
           <t>Малооблачно, без осадков</t>
@@ -11910,96 +11910,96 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Малооблачно, небольшой  дождь</t>
+          <t>Ясно</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>Малооблачно, небольшой  дождь</t>
+          <t>Малооблачно,  дождь</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
           <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>Пасмурно,  дождь</t>
-        </is>
-      </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>Пасмурно, небольшой  дождь</t>
+          <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="B99" t="n">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>21</v>
+      </c>
+      <c r="D99" t="n">
         <v>19</v>
       </c>
-      <c r="C99" t="n">
-        <v>20</v>
-      </c>
-      <c r="D99" t="n">
-        <v>22</v>
-      </c>
       <c r="E99" t="n">
+        <v>21</v>
+      </c>
+      <c r="F99" t="n">
         <v>24</v>
       </c>
-      <c r="F99" t="n">
-        <v>20</v>
-      </c>
       <c r="G99" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H99" t="n">
         <v>16</v>
       </c>
       <c r="I99" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J99" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K99" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M99" t="n">
+        <v>10</v>
+      </c>
+      <c r="N99" t="n">
+        <v>12</v>
+      </c>
+      <c r="O99" t="n">
+        <v>13</v>
+      </c>
+      <c r="P99" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>14</v>
+      </c>
+      <c r="R99" t="n">
         <v>11</v>
       </c>
-      <c r="N99" t="n">
+      <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="T99" t="n">
         <v>10</v>
       </c>
-      <c r="O99" t="n">
-        <v>12</v>
-      </c>
-      <c r="P99" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>11</v>
-      </c>
-      <c r="R99" t="n">
+      <c r="U99" t="n">
         <v>8</v>
       </c>
-      <c r="S99" t="n">
-        <v>9</v>
-      </c>
-      <c r="T99" t="n">
-        <v>14</v>
-      </c>
-      <c r="U99" t="n">
-        <v>13</v>
-      </c>
       <c r="V99" t="inlineStr">
         <is>
           <t>Малооблачно, без осадков</t>
@@ -12007,34 +12007,34 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Малооблачно,  дождь, гроза</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
           <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Ясно</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Ясно</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Малооблачно,  дождь</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>Малооблачно, без осадков</t>
-        </is>
-      </c>
       <c r="AC99" t="inlineStr">
         <is>
           <t>Облачно, небольшой  дождь</t>
@@ -12042,712 +12042,946 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Облачно, небольшой  дождь</t>
+          <t>Пасмурно,  дождь</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Облачно, небольшой  дождь</t>
+          <t>Пасмурно, небольшой  дождь</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="B100" t="n">
+        <v>19</v>
+      </c>
+      <c r="C100" t="n">
         <v>20</v>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>22</v>
       </c>
-      <c r="D100" t="n">
+      <c r="E100" t="n">
         <v>24</v>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>20</v>
       </c>
-      <c r="F100" t="n">
-        <v>17</v>
-      </c>
       <c r="G100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H100" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I100" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J100" t="n">
         <v>21</v>
       </c>
       <c r="K100" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L100" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M100" t="n">
         <v>11</v>
       </c>
       <c r="N100" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P100" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q100" t="n">
         <v>11</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>9</v>
       </c>
       <c r="R100" t="n">
         <v>8</v>
       </c>
       <c r="S100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T100" t="n">
         <v>14</v>
       </c>
       <c r="U100" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
           <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
         <is>
           <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>Малооблачно, небольшой  дождь</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>Малооблачно,  дождь</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>Малооблачно, без осадков</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>Малооблачно, без осадков</t>
-        </is>
-      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Пасмурно, небольшой  дождь</t>
+          <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Малооблачно, небольшой  дождь</t>
+          <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B101" t="n">
+        <v>20</v>
+      </c>
+      <c r="C101" t="n">
         <v>22</v>
       </c>
-      <c r="C101" t="n">
-        <v>25</v>
-      </c>
       <c r="D101" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E101" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F101" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G101" t="n">
         <v>17</v>
       </c>
       <c r="H101" t="n">
+        <v>18</v>
+      </c>
+      <c r="I101" t="n">
         <v>20</v>
       </c>
-      <c r="I101" t="n">
-        <v>19</v>
-      </c>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K101" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L101" t="n">
+        <v>12</v>
+      </c>
+      <c r="M101" t="n">
         <v>11</v>
       </c>
-      <c r="M101" t="n">
-        <v>13</v>
-      </c>
       <c r="N101" t="n">
         <v>13</v>
       </c>
       <c r="O101" t="n">
+        <v>13</v>
+      </c>
+      <c r="P101" t="n">
         <v>11</v>
       </c>
-      <c r="P101" t="n">
+      <c r="Q101" t="n">
+        <v>9</v>
+      </c>
+      <c r="R101" t="n">
         <v>8</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>6</v>
-      </c>
-      <c r="R101" t="n">
-        <v>9</v>
       </c>
       <c r="S101" t="n">
         <v>11</v>
       </c>
       <c r="T101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U101" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Ясно</t>
-        </is>
-      </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Облачно, небольшой  дождь</t>
+          <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>Облачно, небольшой  дождь</t>
+          <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
+          <t>Малооблачно,  дождь</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
           <t>Малооблачно, без осадков</t>
         </is>
       </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>Ясно</t>
-        </is>
-      </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>Ясно</t>
+          <t>Малооблачно, без осадков</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ясно</t>
+          <t>Малооблачно, без осадков</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Пасмурно, небольшой  дождь</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B102" t="n">
+        <v>22</v>
+      </c>
+      <c r="C102" t="n">
         <v>25</v>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>19</v>
       </c>
-      <c r="D102" t="n">
-        <v>16</v>
-      </c>
       <c r="E102" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F102" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G102" t="n">
+        <v>17</v>
+      </c>
+      <c r="H102" t="n">
         <v>20</v>
       </c>
-      <c r="H102" t="n">
-        <v>17</v>
-      </c>
       <c r="I102" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J102" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K102" t="n">
         <v>21</v>
       </c>
       <c r="L102" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M102" t="n">
         <v>13</v>
       </c>
       <c r="N102" t="n">
+        <v>13</v>
+      </c>
+      <c r="O102" t="n">
         <v>11</v>
       </c>
-      <c r="O102" t="n">
+      <c r="P102" t="n">
         <v>8</v>
       </c>
-      <c r="P102" t="n">
+      <c r="Q102" t="n">
         <v>6</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="R102" t="n">
+        <v>9</v>
+      </c>
+      <c r="S102" t="n">
         <v>11</v>
       </c>
-      <c r="R102" t="n">
+      <c r="T102" t="n">
+        <v>10</v>
+      </c>
+      <c r="U102" t="n">
         <v>11</v>
       </c>
-      <c r="S102" t="n">
-        <v>10</v>
-      </c>
-      <c r="T102" t="n">
-        <v>12</v>
-      </c>
-      <c r="U102" t="n">
-        <v>13</v>
-      </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>Skaidrs</t>
+          <t>Ясно</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Mākoņains, neliels  lietus</t>
+          <t>Ясно</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Mazmākoņains, neliels  lietus</t>
+          <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>Mazmākoņains, neliels lietus</t>
+          <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>Skaidrs</t>
+          <t>Малооблачно, без осадков</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Mazmākoņains, neliels lietus</t>
+          <t>Ясно</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Mākoņains, neliels  lietus</t>
+          <t>Ясно</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Mākoņains, neliels  lietus</t>
+          <t>Ясно</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Mazmākoņains, neliels  lietus</t>
+          <t>Малооблачно, без осадков</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>Mazmākoņains, neliels  lietus</t>
+          <t>Малооблачно, без осадков</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B103" t="n">
+        <v>25</v>
+      </c>
+      <c r="C103" t="n">
         <v>19</v>
       </c>
-      <c r="C103" t="n">
-        <v>16</v>
-      </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
+        <v>18</v>
+      </c>
+      <c r="G103" t="n">
+        <v>20</v>
+      </c>
+      <c r="H103" t="n">
+        <v>17</v>
+      </c>
+      <c r="I103" t="n">
+        <v>18</v>
+      </c>
+      <c r="J103" t="n">
+        <v>23</v>
+      </c>
+      <c r="K103" t="n">
         <v>21</v>
       </c>
-      <c r="G103" t="n">
-        <v>16</v>
-      </c>
-      <c r="H103" t="n">
-        <v>13</v>
-      </c>
-      <c r="I103" t="n">
-        <v>12</v>
-      </c>
-      <c r="J103" t="n">
-        <v>15</v>
-      </c>
-      <c r="K103" t="n">
-        <v>15</v>
-      </c>
       <c r="L103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M103" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N103" t="n">
+        <v>11</v>
+      </c>
+      <c r="O103" t="n">
         <v>8</v>
       </c>
-      <c r="O103" t="n">
+      <c r="P103" t="n">
         <v>6</v>
-      </c>
-      <c r="P103" t="n">
-        <v>9</v>
       </c>
       <c r="Q103" t="n">
         <v>11</v>
       </c>
       <c r="R103" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T103" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U103" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Малооблачно, небольшой  дождь</t>
+          <t>Skaidrs</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Малооблачно, небольшой  дождь</t>
+          <t>Mākoņains, neliels  lietus</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Mazmākoņains, neliels  lietus</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>Ясно</t>
+          <t>Mazmākoņains, neliels lietus</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>Ясно</t>
+          <t>Skaidrs</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Облачно,  дождь</t>
+          <t>Mazmākoņains, neliels lietus</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>Пасмурно, небольшой  дождь</t>
+          <t>Mākoņains, neliels  lietus</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Пасмурно, небольшой  дождь</t>
+          <t>Mākoņains, neliels  lietus</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Пасмурно,  дождь</t>
+          <t>Mazmākoņains, neliels  lietus</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>Пасмурно, небольшой  дождь</t>
+          <t>Mazmākoņains, neliels  lietus</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D104" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E104" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F104" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G104" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H104" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I104" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J104" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K104" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L104" t="n">
+        <v>13</v>
+      </c>
+      <c r="M104" t="n">
+        <v>10</v>
+      </c>
+      <c r="N104" t="n">
+        <v>8</v>
+      </c>
+      <c r="O104" t="n">
+        <v>6</v>
+      </c>
+      <c r="P104" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q104" t="n">
         <v>11</v>
       </c>
-      <c r="M104" t="n">
+      <c r="R104" t="n">
         <v>9</v>
       </c>
-      <c r="N104" t="n">
-        <v>4</v>
-      </c>
-      <c r="O104" t="n">
+      <c r="S104" t="n">
         <v>8</v>
       </c>
-      <c r="P104" t="n">
+      <c r="T104" t="n">
+        <v>7</v>
+      </c>
+      <c r="U104" t="n">
         <v>11</v>
       </c>
-      <c r="Q104" t="n">
-        <v>10</v>
-      </c>
-      <c r="R104" t="n">
-        <v>7</v>
-      </c>
-      <c r="S104" t="n">
-        <v>9</v>
-      </c>
-      <c r="T104" t="n">
-        <v>10</v>
-      </c>
-      <c r="U104" t="n">
-        <v>13</v>
-      </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Облачно, небольшой  дождь</t>
+          <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
           <t>Малооблачно, без осадков</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Облачно, небольшой  дождь</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Облачно,  дождь</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>Ясно</t>
+          <t>Пасмурно, небольшой  дождь</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Пасмурно, небольшой  дождь</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Ясно</t>
+          <t>Пасмурно,  дождь</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Малооблачно, без осадков</t>
+          <t>Пасмурно, небольшой  дождь</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>15</v>
+      </c>
+      <c r="D105" t="n">
+        <v>18</v>
+      </c>
+      <c r="E105" t="n">
+        <v>22</v>
+      </c>
+      <c r="F105" t="n">
+        <v>17</v>
+      </c>
+      <c r="G105" t="n">
+        <v>17</v>
+      </c>
+      <c r="H105" t="n">
+        <v>17</v>
+      </c>
+      <c r="I105" t="n">
+        <v>17</v>
+      </c>
+      <c r="J105" t="n">
+        <v>21</v>
+      </c>
+      <c r="K105" t="n">
+        <v>22</v>
+      </c>
+      <c r="L105" t="n">
+        <v>11</v>
+      </c>
+      <c r="M105" t="n">
+        <v>9</v>
+      </c>
+      <c r="N105" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" t="n">
+        <v>8</v>
+      </c>
+      <c r="P105" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>10</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7</v>
+      </c>
+      <c r="S105" t="n">
+        <v>9</v>
+      </c>
+      <c r="T105" t="n">
+        <v>10</v>
+      </c>
+      <c r="U105" t="n">
+        <v>13</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
           <t>2024-08-31</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>15</v>
-      </c>
-      <c r="C105" t="n">
-        <v>17</v>
-      </c>
-      <c r="D105" t="n">
+      <c r="B106" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" t="n">
+        <v>17</v>
+      </c>
+      <c r="D106" t="n">
         <v>21</v>
       </c>
-      <c r="E105" t="n">
-        <v>16</v>
-      </c>
-      <c r="F105" t="n">
-        <v>13</v>
-      </c>
-      <c r="G105" t="n">
+      <c r="E106" t="n">
+        <v>16</v>
+      </c>
+      <c r="F106" t="n">
+        <v>13</v>
+      </c>
+      <c r="G106" t="n">
         <v>14</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H106" t="n">
         <v>14</v>
       </c>
-      <c r="I105" t="n">
-        <v>18</v>
-      </c>
-      <c r="J105" t="n">
+      <c r="I106" t="n">
+        <v>18</v>
+      </c>
+      <c r="J106" t="n">
         <v>19</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K106" t="n">
         <v>19</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L106" t="n">
         <v>8</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M106" t="n">
         <v>6</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N106" t="n">
         <v>9</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O106" t="n">
         <v>10</v>
       </c>
-      <c r="P105" t="n">
+      <c r="P106" t="n">
         <v>8</v>
       </c>
-      <c r="Q105" t="n">
+      <c r="Q106" t="n">
         <v>6</v>
       </c>
-      <c r="R105" t="n">
+      <c r="R106" t="n">
         <v>8</v>
       </c>
-      <c r="S105" t="n">
+      <c r="S106" t="n">
         <v>8</v>
       </c>
-      <c r="T105" t="n">
+      <c r="T106" t="n">
         <v>9</v>
       </c>
-      <c r="U105" t="n">
+      <c r="U106" t="n">
         <v>10</v>
       </c>
-      <c r="V105" t="inlineStr">
+      <c r="V106" t="inlineStr">
         <is>
           <t>Облачно, без осадков</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr">
+      <c r="W106" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>Облачно, без осадков</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="AA105" t="inlineStr">
+      <c r="AA106" t="inlineStr">
         <is>
           <t>Облачно, без осадков</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AB106" t="inlineStr">
         <is>
           <t>Облачно, небольшой  дождь</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
+      <c r="AC106" t="inlineStr">
         <is>
           <t>Малооблачно,  дождь</t>
         </is>
       </c>
-      <c r="AD105" t="inlineStr">
+      <c r="AD106" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
       </c>
-      <c r="AE105" t="inlineStr">
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>17</v>
+      </c>
+      <c r="C107" t="n">
+        <v>19</v>
+      </c>
+      <c r="D107" t="n">
+        <v>16</v>
+      </c>
+      <c r="E107" t="n">
+        <v>12</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13</v>
+      </c>
+      <c r="G107" t="n">
+        <v>18</v>
+      </c>
+      <c r="H107" t="n">
+        <v>18</v>
+      </c>
+      <c r="I107" t="n">
+        <v>23</v>
+      </c>
+      <c r="J107" t="n">
+        <v>22</v>
+      </c>
+      <c r="K107" t="n">
+        <v>20</v>
+      </c>
+      <c r="L107" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>9</v>
+      </c>
+      <c r="N107" t="n">
+        <v>10</v>
+      </c>
+      <c r="O107" t="n">
+        <v>8</v>
+      </c>
+      <c r="P107" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>8</v>
+      </c>
+      <c r="R107" t="n">
+        <v>10</v>
+      </c>
+      <c r="S107" t="n">
+        <v>14</v>
+      </c>
+      <c r="T107" t="n">
+        <v>15</v>
+      </c>
+      <c r="U107" t="n">
+        <v>13</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>

--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE107"/>
+  <dimension ref="A1:AE110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12984,6 +12984,357 @@
       <c r="AE107" t="inlineStr">
         <is>
           <t>Ясно</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>19</v>
+      </c>
+      <c r="C108" t="n">
+        <v>16</v>
+      </c>
+      <c r="D108" t="n">
+        <v>13</v>
+      </c>
+      <c r="E108" t="n">
+        <v>14</v>
+      </c>
+      <c r="F108" t="n">
+        <v>19</v>
+      </c>
+      <c r="G108" t="n">
+        <v>21</v>
+      </c>
+      <c r="H108" t="n">
+        <v>20</v>
+      </c>
+      <c r="I108" t="n">
+        <v>21</v>
+      </c>
+      <c r="J108" t="n">
+        <v>21</v>
+      </c>
+      <c r="K108" t="n">
+        <v>19</v>
+      </c>
+      <c r="L108" t="n">
+        <v>9</v>
+      </c>
+      <c r="M108" t="n">
+        <v>10</v>
+      </c>
+      <c r="N108" t="n">
+        <v>9</v>
+      </c>
+      <c r="O108" t="n">
+        <v>8</v>
+      </c>
+      <c r="P108" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>12</v>
+      </c>
+      <c r="R108" t="n">
+        <v>12</v>
+      </c>
+      <c r="S108" t="n">
+        <v>13</v>
+      </c>
+      <c r="T108" t="n">
+        <v>13</v>
+      </c>
+      <c r="U108" t="n">
+        <v>15</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Пасмурно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>13</v>
+      </c>
+      <c r="D109" t="n">
+        <v>14</v>
+      </c>
+      <c r="E109" t="n">
+        <v>18</v>
+      </c>
+      <c r="F109" t="n">
+        <v>17</v>
+      </c>
+      <c r="G109" t="n">
+        <v>20</v>
+      </c>
+      <c r="H109" t="n">
+        <v>22</v>
+      </c>
+      <c r="I109" t="n">
+        <v>20</v>
+      </c>
+      <c r="J109" t="n">
+        <v>21</v>
+      </c>
+      <c r="K109" t="n">
+        <v>19</v>
+      </c>
+      <c r="L109" t="n">
+        <v>11</v>
+      </c>
+      <c r="M109" t="n">
+        <v>9</v>
+      </c>
+      <c r="N109" t="n">
+        <v>9</v>
+      </c>
+      <c r="O109" t="n">
+        <v>8</v>
+      </c>
+      <c r="P109" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>12</v>
+      </c>
+      <c r="R109" t="n">
+        <v>13</v>
+      </c>
+      <c r="S109" t="n">
+        <v>13</v>
+      </c>
+      <c r="T109" t="n">
+        <v>13</v>
+      </c>
+      <c r="U109" t="n">
+        <v>12</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>13</v>
+      </c>
+      <c r="C110" t="n">
+        <v>14</v>
+      </c>
+      <c r="D110" t="n">
+        <v>18</v>
+      </c>
+      <c r="E110" t="n">
+        <v>18</v>
+      </c>
+      <c r="F110" t="n">
+        <v>23</v>
+      </c>
+      <c r="G110" t="n">
+        <v>22</v>
+      </c>
+      <c r="H110" t="n">
+        <v>21</v>
+      </c>
+      <c r="I110" t="n">
+        <v>20</v>
+      </c>
+      <c r="J110" t="n">
+        <v>20</v>
+      </c>
+      <c r="K110" t="n">
+        <v>16</v>
+      </c>
+      <c r="L110" t="n">
+        <v>9</v>
+      </c>
+      <c r="M110" t="n">
+        <v>9</v>
+      </c>
+      <c r="N110" t="n">
+        <v>8</v>
+      </c>
+      <c r="O110" t="n">
+        <v>12</v>
+      </c>
+      <c r="P110" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>12</v>
+      </c>
+      <c r="R110" t="n">
+        <v>13</v>
+      </c>
+      <c r="S110" t="n">
+        <v>12</v>
+      </c>
+      <c r="T110" t="n">
+        <v>11</v>
+      </c>
+      <c r="U110" t="n">
+        <v>11</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Пасмурно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Облачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
         </is>
       </c>
     </row>

--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE110"/>
+  <dimension ref="A1:AE111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13335,6 +13335,123 @@
       <c r="AE110" t="inlineStr">
         <is>
           <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>12</v>
+      </c>
+      <c r="C111" t="n">
+        <v>18</v>
+      </c>
+      <c r="D111" t="n">
+        <v>16</v>
+      </c>
+      <c r="E111" t="n">
+        <v>21</v>
+      </c>
+      <c r="F111" t="n">
+        <v>22</v>
+      </c>
+      <c r="G111" t="n">
+        <v>22</v>
+      </c>
+      <c r="H111" t="n">
+        <v>20</v>
+      </c>
+      <c r="I111" t="n">
+        <v>20</v>
+      </c>
+      <c r="J111" t="n">
+        <v>18</v>
+      </c>
+      <c r="K111" t="n">
+        <v>17</v>
+      </c>
+      <c r="L111" t="n">
+        <v>8</v>
+      </c>
+      <c r="M111" t="n">
+        <v>9</v>
+      </c>
+      <c r="N111" t="n">
+        <v>12</v>
+      </c>
+      <c r="O111" t="n">
+        <v>10</v>
+      </c>
+      <c r="P111" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>12</v>
+      </c>
+      <c r="R111" t="n">
+        <v>13</v>
+      </c>
+      <c r="S111" t="n">
+        <v>12</v>
+      </c>
+      <c r="T111" t="n">
+        <v>12</v>
+      </c>
+      <c r="U111" t="n">
+        <v>10</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Облачно,  дождь</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>Малооблачно,  дождь, гроза</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>Ясно</t>
         </is>
       </c>
     </row>

--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE111"/>
+  <dimension ref="A1:AE112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13450,6 +13450,123 @@
         </is>
       </c>
       <c r="AE111" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>14</v>
+      </c>
+      <c r="C112" t="n">
+        <v>16</v>
+      </c>
+      <c r="D112" t="n">
+        <v>23</v>
+      </c>
+      <c r="E112" t="n">
+        <v>22</v>
+      </c>
+      <c r="F112" t="n">
+        <v>22</v>
+      </c>
+      <c r="G112" t="n">
+        <v>21</v>
+      </c>
+      <c r="H112" t="n">
+        <v>21</v>
+      </c>
+      <c r="I112" t="n">
+        <v>18</v>
+      </c>
+      <c r="J112" t="n">
+        <v>17</v>
+      </c>
+      <c r="K112" t="n">
+        <v>12</v>
+      </c>
+      <c r="L112" t="n">
+        <v>6</v>
+      </c>
+      <c r="M112" t="n">
+        <v>12</v>
+      </c>
+      <c r="N112" t="n">
+        <v>11</v>
+      </c>
+      <c r="O112" t="n">
+        <v>14</v>
+      </c>
+      <c r="P112" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>13</v>
+      </c>
+      <c r="R112" t="n">
+        <v>12</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="n">
+        <v>10</v>
+      </c>
+      <c r="U112" t="n">
+        <v>6</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Облачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь, гроза</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>

--- a/data/Ekaterinburg_GisMeteo_10.xlsx
+++ b/data/Ekaterinburg_GisMeteo_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE112"/>
+  <dimension ref="A1:AE114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13567,6 +13567,240 @@
         </is>
       </c>
       <c r="AE112" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>23</v>
+      </c>
+      <c r="C113" t="n">
+        <v>22</v>
+      </c>
+      <c r="D113" t="n">
+        <v>22</v>
+      </c>
+      <c r="E113" t="n">
+        <v>19</v>
+      </c>
+      <c r="F113" t="n">
+        <v>20</v>
+      </c>
+      <c r="G113" t="n">
+        <v>19</v>
+      </c>
+      <c r="H113" t="n">
+        <v>20</v>
+      </c>
+      <c r="I113" t="n">
+        <v>17</v>
+      </c>
+      <c r="J113" t="n">
+        <v>17</v>
+      </c>
+      <c r="K113" t="n">
+        <v>16</v>
+      </c>
+      <c r="L113" t="n">
+        <v>10</v>
+      </c>
+      <c r="M113" t="n">
+        <v>14</v>
+      </c>
+      <c r="N113" t="n">
+        <v>12</v>
+      </c>
+      <c r="O113" t="n">
+        <v>11</v>
+      </c>
+      <c r="P113" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>9</v>
+      </c>
+      <c r="R113" t="n">
+        <v>9</v>
+      </c>
+      <c r="S113" t="n">
+        <v>11</v>
+      </c>
+      <c r="T113" t="n">
+        <v>10</v>
+      </c>
+      <c r="U113" t="n">
+        <v>9</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>23</v>
+      </c>
+      <c r="C114" t="n">
+        <v>22</v>
+      </c>
+      <c r="D114" t="n">
+        <v>22</v>
+      </c>
+      <c r="E114" t="n">
+        <v>19</v>
+      </c>
+      <c r="F114" t="n">
+        <v>19</v>
+      </c>
+      <c r="G114" t="n">
+        <v>19</v>
+      </c>
+      <c r="H114" t="n">
+        <v>20</v>
+      </c>
+      <c r="I114" t="n">
+        <v>18</v>
+      </c>
+      <c r="J114" t="n">
+        <v>18</v>
+      </c>
+      <c r="K114" t="n">
+        <v>17</v>
+      </c>
+      <c r="L114" t="n">
+        <v>10</v>
+      </c>
+      <c r="M114" t="n">
+        <v>14</v>
+      </c>
+      <c r="N114" t="n">
+        <v>13</v>
+      </c>
+      <c r="O114" t="n">
+        <v>11</v>
+      </c>
+      <c r="P114" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>9</v>
+      </c>
+      <c r="R114" t="n">
+        <v>9</v>
+      </c>
+      <c r="S114" t="n">
+        <v>9</v>
+      </c>
+      <c r="T114" t="n">
+        <v>12</v>
+      </c>
+      <c r="U114" t="n">
+        <v>10</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>Ясно</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Малооблачно, небольшой  дождь</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>Малооблачно, без осадков</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
         <is>
           <t>Ясно</t>
         </is>
